--- a/DATA_DANTON_DANKI.xlsx
+++ b/DATA_DANTON_DANKI.xlsx
@@ -1,17 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rifaldianggarapurwadi/Downloads/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7346E2F4-EA14-5A47-B786-CF39B447580C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="16800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="64">
   <si>
     <t>NO</t>
   </si>
@@ -201,29 +210,45 @@
   </si>
   <si>
     <t>92100029</t>
+  </si>
+  <si>
+    <t>01111489</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color rgb="FF002060"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF002060"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -231,7 +256,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -241,7 +266,13 @@
     </fill>
   </fills>
   <borders count="3">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -249,75 +280,70 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="11">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="top"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="top"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" vertical="top"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="0"/>
-    </xf>
-    <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -325,7 +351,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -515,23 +541,26 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="22.63"/>
-    <col customWidth="1" min="2" max="2" width="60.13"/>
-    <col customWidth="1" min="4" max="4" width="30.75"/>
-    <col customWidth="1" min="5" max="5" width="29.25"/>
+    <col min="1" max="1" width="22.6640625" customWidth="1"/>
+    <col min="2" max="2" width="60.1640625" customWidth="1"/>
+    <col min="4" max="4" width="30.6640625" customWidth="1"/>
+    <col min="5" max="5" width="29.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -541,337 +570,337 @@
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="4">
-        <v>1.0</v>
-      </c>
-      <c r="B2" s="5" t="s">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" s="3">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="9">
-        <v>2.0</v>
-      </c>
-      <c r="B3" s="10" t="s">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" s="3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="9">
-        <v>3.0</v>
-      </c>
-      <c r="B4" s="10" t="s">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" s="3">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="4">
-        <v>4.0</v>
-      </c>
-      <c r="B5" s="10" t="s">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" s="3">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="6" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="B6" s="5" t="s">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" s="3">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="E6" s="7" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="9">
-        <v>6.0</v>
-      </c>
-      <c r="B7" s="10" t="s">
+    <row r="7" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A7" s="3">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7" s="7" t="s">
+      <c r="C7" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="10" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8" s="3">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9" s="3">
+        <v>8</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A10" s="3">
+        <v>9</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11" s="3">
+        <v>10</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A12" s="3">
+        <v>11</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13" s="3">
+        <v>12</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14" s="3">
+        <v>13</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A15" s="3">
+        <v>14</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A16" s="3">
+        <v>15</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17" s="3">
+        <v>16</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E17" s="6" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="9">
-        <v>7.0</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4">
-        <v>8.0</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="9">
-        <v>9.0</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="9">
-        <v>10.0</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="E11" s="11" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4">
-        <v>11.0</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="E12" s="11" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="9">
-        <v>12.0</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="C13" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="E13" s="11" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="9">
-        <v>13.0</v>
-      </c>
-      <c r="B14" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="E14" s="11" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4">
-        <v>14.0</v>
-      </c>
-      <c r="B15" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="E15" s="11" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="9">
-        <v>15.0</v>
-      </c>
-      <c r="B16" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="E16" s="11" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="9">
-        <v>16.0</v>
-      </c>
-      <c r="B17" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4">
-        <v>17.0</v>
-      </c>
-      <c r="B18" s="10" t="s">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A18" s="3">
+        <v>17</v>
+      </c>
+      <c r="B18" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C18" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D18" s="7" t="s">
+      <c r="C18" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D18" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="E18" s="11" t="s">
+      <c r="E18" s="7" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="9">
-        <v>18.0</v>
-      </c>
-      <c r="B19" s="10" t="s">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A19" s="3">
+        <v>18</v>
+      </c>
+      <c r="B19" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C19" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D19" s="7" t="s">
+      <c r="C19" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D19" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="E19" s="11" t="s">
+      <c r="E19" s="7" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="9">
-        <v>19.0</v>
-      </c>
-      <c r="B20" s="10" t="s">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20" s="3">
+        <v>19</v>
+      </c>
+      <c r="B20" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="C20" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D20" s="7" t="s">
+      <c r="C20" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D20" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="E20" s="11" t="s">
+      <c r="E20" s="7" t="s">
         <v>62</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/DATA_DANTON_DANKI.xlsx
+++ b/DATA_DANTON_DANKI.xlsx
@@ -1,26 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rifaldianggarapurwadi/Downloads/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69DE085A-F5F0-9E44-8FE8-4C3A81E1BA9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="16880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="63">
   <si>
     <t>NO</t>
   </si>
@@ -113,6 +104,9 @@
   </si>
   <si>
     <t>92050091</t>
+  </si>
+  <si>
+    <t>MUHAMMAD ALIF FADILLAH, S.Tr.K.</t>
   </si>
   <si>
     <t>DANTON TAR 1/II</t>
@@ -167,6 +161,9 @@
     <t>01101509</t>
   </si>
   <si>
+    <t>FATIR ALAM, S.Tr.K.</t>
+  </si>
+  <si>
     <t>DANTON TAR 2/IV</t>
   </si>
   <si>
@@ -204,40 +201,29 @@
   </si>
   <si>
     <t>92100029</t>
-  </si>
-  <si>
-    <t>01111489</t>
-  </si>
-  <si>
-    <t>FATIR ALAM, S.Tr.K., M.H.</t>
-  </si>
-  <si>
-    <t>MUHAMMAD ALIF FADILLAH, S.Tr.K., M.A.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <fonts count="3">
     <font>
-      <sz val="10"/>
+      <sz val="10.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
+      <sz val="12.0"/>
       <color rgb="FF002060"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="12.0"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -245,7 +231,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="lightGray"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -255,13 +241,7 @@
     </fill>
   </fills>
   <borders count="3">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+    <border/>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -269,64 +249,75 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
-      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
-      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
-      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="9">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+  <cellXfs count="14">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="top"/>
+    </xf>
+    <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="top"/>
+    </xf>
+    <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" vertical="top"/>
+    </xf>
+    <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="0"/>
+    </xf>
+    <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
+    </xf>
+    <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -334,7 +325,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -524,26 +515,23 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="22.6640625" customWidth="1"/>
-    <col min="2" max="2" width="60.1640625" customWidth="1"/>
-    <col min="4" max="4" width="30.6640625" customWidth="1"/>
-    <col min="5" max="5" width="29.1640625" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="22.63"/>
+    <col customWidth="1" min="2" max="2" width="60.13"/>
+    <col customWidth="1" min="4" max="4" width="30.75"/>
+    <col customWidth="1" min="5" max="5" width="29.25"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -553,337 +541,337 @@
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="3">
-        <v>1</v>
-      </c>
-      <c r="B2" s="4" t="s">
+    <row r="2">
+      <c r="A2" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="8" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3" s="3">
-        <v>2</v>
-      </c>
-      <c r="B3" s="4" t="s">
+    <row r="3">
+      <c r="A3" s="9">
+        <v>2.0</v>
+      </c>
+      <c r="B3" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A4" s="3">
-        <v>3</v>
-      </c>
-      <c r="B4" s="4" t="s">
+    <row r="4">
+      <c r="A4" s="9">
+        <v>3.0</v>
+      </c>
+      <c r="B4" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="8" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A5" s="3">
-        <v>4</v>
-      </c>
-      <c r="B5" s="4" t="s">
+    <row r="5">
+      <c r="A5" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="B5" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="8" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A6" s="3">
-        <v>5</v>
-      </c>
-      <c r="B6" s="4" t="s">
+    <row r="6">
+      <c r="A6" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="11" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A7" s="3">
-        <v>6</v>
-      </c>
-      <c r="B7" s="4" t="s">
+    <row r="7">
+      <c r="A7" s="9">
+        <v>6.0</v>
+      </c>
+      <c r="B7" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7" s="5" t="s">
+      <c r="C7" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9">
+        <v>7.0</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4">
+        <v>8.0</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9">
+        <v>9.0</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9">
+        <v>10.0</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4">
+        <v>11.0</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9">
+        <v>12.0</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9">
+        <v>13.0</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4">
+        <v>14.0</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9">
+        <v>15.0</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9">
+        <v>16.0</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4">
+        <v>17.0</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9">
+        <v>18.0</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9">
+        <v>19.0</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D20" s="7" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A8" s="3">
-        <v>7</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A9" s="3">
-        <v>8</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A10" s="3">
-        <v>9</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A11" s="3">
-        <v>10</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A12" s="3">
-        <v>11</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A13" s="3">
-        <v>12</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A14" s="3">
-        <v>13</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A15" s="3">
-        <v>14</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A16" s="3">
-        <v>15</v>
-      </c>
-      <c r="B16" s="8" t="s">
+      <c r="E20" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="C16" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A17" s="3">
-        <v>16</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A18" s="3">
-        <v>17</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A19" s="3">
-        <v>18</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A20" s="3">
-        <v>19</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>60</v>
-      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/DATA_DANTON_DANKI.xlsx
+++ b/DATA_DANTON_DANKI.xlsx
@@ -1,17 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rifaldianggarapurwadi/Downloads/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69DE085A-F5F0-9E44-8FE8-4C3A81E1BA9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="16880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="64">
   <si>
     <t>NO</t>
   </si>
@@ -104,9 +113,6 @@
   </si>
   <si>
     <t>92050091</t>
-  </si>
-  <si>
-    <t>MUHAMMAD ALIF FADILLAH, S.Tr.K.</t>
   </si>
   <si>
     <t>DANTON TAR 1/II</t>
@@ -161,9 +167,6 @@
     <t>01101509</t>
   </si>
   <si>
-    <t>FATIR ALAM, S.Tr.K.</t>
-  </si>
-  <si>
     <t>DANTON TAR 2/IV</t>
   </si>
   <si>
@@ -201,29 +204,40 @@
   </si>
   <si>
     <t>92100029</t>
+  </si>
+  <si>
+    <t>01111489</t>
+  </si>
+  <si>
+    <t>FATIR ALAM, S.Tr.K., M.H.</t>
+  </si>
+  <si>
+    <t>MUHAMMAD ALIF FADILLAH, S.Tr.K., M.A.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color rgb="FF002060"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -231,7 +245,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -241,7 +255,13 @@
     </fill>
   </fills>
   <borders count="3">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -249,75 +269,64 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="9">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="top"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="top"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" vertical="top"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="0"/>
-    </xf>
-    <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -325,7 +334,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -515,23 +524,26 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="22.63"/>
-    <col customWidth="1" min="2" max="2" width="60.13"/>
-    <col customWidth="1" min="4" max="4" width="30.75"/>
-    <col customWidth="1" min="5" max="5" width="29.25"/>
+    <col min="1" max="1" width="22.6640625" customWidth="1"/>
+    <col min="2" max="2" width="60.1640625" customWidth="1"/>
+    <col min="4" max="4" width="30.6640625" customWidth="1"/>
+    <col min="5" max="5" width="29.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -541,337 +553,337 @@
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="4">
-        <v>1.0</v>
-      </c>
-      <c r="B2" s="5" t="s">
+    <row r="2" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" s="3">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="9">
-        <v>2.0</v>
-      </c>
-      <c r="B3" s="10" t="s">
+    <row r="3" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A3" s="3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="9">
-        <v>3.0</v>
-      </c>
-      <c r="B4" s="10" t="s">
+    <row r="4" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A4" s="3">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="4">
-        <v>4.0</v>
-      </c>
-      <c r="B5" s="10" t="s">
+    <row r="5" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A5" s="3">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="6" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="B6" s="5" t="s">
+    <row r="6" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A6" s="3">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="E6" s="7" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="9">
-        <v>6.0</v>
-      </c>
-      <c r="B7" s="10" t="s">
+    <row r="7" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A7" s="3">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7" s="7" t="s">
+      <c r="C7" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="6" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A8" s="3">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A9" s="3">
+        <v>8</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A10" s="3">
+        <v>9</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A11" s="3">
+        <v>10</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A12" s="3">
+        <v>11</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A13" s="3">
+        <v>12</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A14" s="3">
+        <v>13</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A15" s="3">
+        <v>14</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A16" s="3">
+        <v>15</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A17" s="3">
+        <v>16</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E17" s="6" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="9">
-        <v>7.0</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4">
-        <v>8.0</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="9">
-        <v>9.0</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="9">
-        <v>10.0</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="E11" s="11" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4">
-        <v>11.0</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="E12" s="11" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="9">
-        <v>12.0</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="C13" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="E13" s="11" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="9">
-        <v>13.0</v>
-      </c>
-      <c r="B14" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="E14" s="11" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4">
-        <v>14.0</v>
-      </c>
-      <c r="B15" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="E15" s="11" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="9">
-        <v>15.0</v>
-      </c>
-      <c r="B16" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="E16" s="11" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="9">
-        <v>16.0</v>
-      </c>
-      <c r="B17" s="10" t="s">
+    <row r="18" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A18" s="3">
+        <v>17</v>
+      </c>
+      <c r="B18" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="C17" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D17" s="7" t="s">
+      <c r="C18" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D18" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="E17" s="8" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4">
-        <v>17.0</v>
-      </c>
-      <c r="B18" s="10" t="s">
+      <c r="E18" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="C18" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D18" s="7" t="s">
+    </row>
+    <row r="19" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A19" s="3">
+        <v>18</v>
+      </c>
+      <c r="B19" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="E18" s="11" t="s">
+      <c r="C19" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D19" s="5" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="9">
-        <v>18.0</v>
-      </c>
-      <c r="B19" s="10" t="s">
+      <c r="E19" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="C19" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D19" s="7" t="s">
+    </row>
+    <row r="20" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A20" s="3">
+        <v>19</v>
+      </c>
+      <c r="B20" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="E19" s="11" t="s">
+      <c r="C20" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D20" s="5" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="9">
-        <v>19.0</v>
-      </c>
-      <c r="B20" s="10" t="s">
+      <c r="E20" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="C20" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="E20" s="11" t="s">
-        <v>62</v>
-      </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/DATA_DANTON_DANKI.xlsx
+++ b/DATA_DANTON_DANKI.xlsx
@@ -56,7 +56,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -78,20 +78,6 @@
         <color rgb="00AAAAAA"/>
       </bottom>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00CCCCCC"/>
-      </left>
-      <right style="thin">
-        <color rgb="00CCCCCC"/>
-      </right>
-      <top style="thin">
-        <color rgb="00CCCCCC"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00CCCCCC"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -101,16 +87,16 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -651,7 +637,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>IPDA</t>
+          <t>IPTU</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -661,7 +647,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>01111489</t>
+          <t>1111489</t>
         </is>
       </c>
     </row>
@@ -726,7 +712,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>IPDA</t>
+          <t>IPTU</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -736,7 +722,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>00111147</t>
+          <t>111147</t>
         </is>
       </c>
     </row>
@@ -801,7 +787,7 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>IPDA</t>
+          <t>IPTU</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
@@ -811,7 +797,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>00020930</t>
+          <t>20930</t>
         </is>
       </c>
     </row>
@@ -861,7 +847,7 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>01101509</t>
+          <t>1101509</t>
         </is>
       </c>
     </row>
@@ -876,7 +862,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>IPDA</t>
+          <t>IPTU</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -961,7 +947,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>01031201</t>
+          <t>1031201</t>
         </is>
       </c>
     </row>
@@ -1038,16 +1024,16 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr">
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="2" t="inlineStr"/>
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>[DATA TK I BELUM TERSEDIA — ISI SESUAI FORMAT]</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+      <c r="C2" s="2" t="inlineStr"/>
+      <c r="D2" s="3" t="inlineStr"/>
+      <c r="E2" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1060,7 +1046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1097,16 +1083,404 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>[DATA TK III BELUM TERSEDIA — ISI SESUAI FORMAT]</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>BAGUS AGUNG SUBAHENDRO, S.Tr.K</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>AKP</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>DANKI TAR A</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="A3" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>AGUNG BUDIMAN, S.T.K., S.I.K.</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>AKP</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>DANKI TAR B</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr"/>
+    </row>
+    <row r="4" ht="16" customHeight="1">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>DIMAS WICAKSONO SIJAYA, S.Tr.K., S.I.K</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>AKP</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>DANKI TAR C</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>IHSAN TIO BASIR, S.Tr.K., S.I.K</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>IPTU</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>DANKI TAR D</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr"/>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>RINA ARYANTI, S.Tr.K., S.I.K.</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>AKP</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>DANKI TAR E</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>FATAHILLAH ASLAM FIRMANSYAH, S.Tr.K. M.Si</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>IPTU</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>DANTON TAR 1A</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>SATRIA ARDI YANA, S.H., M.H.</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>IPDA</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>DANTON TAR 2A</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>ERIAN YUDYA PRASETYA, S.H., M.M.</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>IPDA</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>DANTON TAR 3A</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>MUHAMMAD FADLI, S.Tr.K.</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>IPTU</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>DANTON TAR 1B</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>IMAM SANTOSO, S.H.</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>IPDA</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>DANTON TAR 2B</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr"/>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>MOCH. DAVID ARYA SUSILA PUTRA, S.Tr.K.</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>IPDA</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>DANTON TAR 3B</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>AKBAR QOLBU NOORYONO, S.Tr.K., M.H.</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>IPDA</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>DANTON TAR 1C</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>HERIANSYAH, S.Tr.K</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>IPTU</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>DANTON TAR 2C</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>TEGAR MULIA NST, S.Tr.K</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>IPDA</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>DANTON TAR 3C</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr"/>
+    </row>
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>DIMMAS PRAWIRA PRATAMA, S.Tr.K., S.I.K., M.H.</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>IPTU</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>DANTON TAR 1D</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>GAMA TRAYA AKTIVA S.H., M.H.</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>IPDA</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>DANTON TAR 2D</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr"/>
+    </row>
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>MARZUKI JOSHUA MARPAUNG, S.Tr.K.</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>IPDA</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>DANTON TAR 3D</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>SRI DEVY, S.Tr.K.</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>IPTU</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>DANTON TAR 1E</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr"/>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>INTAN PUSPITASARI, S.H., M.H.</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>IPDA</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>DANTON TAR 2E</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/DATA_DANTON_DANKI.xlsx
+++ b/DATA_DANTON_DANKI.xlsx
@@ -524,7 +524,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>MUHAMMAD RIZQY SAPUTRA, S.T.K., S.I.K., M.Si.</t>
+          <t>DWI ANGGA PRASETYO, S.Tr.K., S.I.K., M.H</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -539,7 +539,7 @@
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>90080303</t>
+          <t>94041309</t>
         </is>
       </c>
     </row>

--- a/DATA_DANTON_DANKI.xlsx
+++ b/DATA_DANTON_DANKI.xlsx
@@ -524,7 +524,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>DWI ANGGA PRASETYO, S.Tr.K., S.I.K., M.H</t>
+          <t>AGUNG BUDIMAN, S.T.K., S.I.K.</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -537,11 +537,7 @@
           <t>DANKI TAR I</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
-        <is>
-          <t>94041309</t>
-        </is>
-      </c>
+      <c r="E2" s="5" t="inlineStr"/>
     </row>
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="6" t="n">

--- a/DATA_DANTON_DANKI.xlsx
+++ b/DATA_DANTON_DANKI.xlsx
@@ -524,7 +524,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>AGUNG BUDIMAN, S.T.K., S.I.K.</t>
+          <t>RANDY ANUGRAH PUTRANTO, S.Tr.K., S.I.K., M.H.</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -537,7 +537,11 @@
           <t>DANKI TAR I</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr"/>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>94081261</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="6" t="n">

--- a/DATA_DANTON_DANKI.xlsx
+++ b/DATA_DANTON_DANKI.xlsx
@@ -849,7 +849,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>AFGHA SATRIYA PRAYOGA, S.Tr.K., M.Si.</t>
+          <t>SUGENG HARYADI, S.Psi., M.Psi.</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>01101509</t>
+          <t>92040084</t>
         </is>
       </c>
     </row>
